--- a/DEMOWEBSHOP/src/test/resources/TestData/Address_TestData.xlsx
+++ b/DEMOWEBSHOP/src/test/resources/TestData/Address_TestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DWS\AUTOMATIONPROJECT\DEMOWEBSHOP\src\test\resources\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AABE7909-5565-48AF-B57D-3B19D0277B3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE6ADA34-677C-4827-90C2-4129B02BCBF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="59">
   <si>
     <t>FirstName</t>
   </si>
@@ -140,13 +140,70 @@
   </si>
   <si>
     <t>tanush@gmail.com</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>Salem</t>
+  </si>
+  <si>
+    <t>Andhra</t>
+  </si>
+  <si>
+    <t>Chennai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dharshan </t>
+  </si>
+  <si>
+    <t>dharshan@gmail.com</t>
+  </si>
+  <si>
+    <t>Expleo</t>
+  </si>
+  <si>
+    <t>Mg road</t>
+  </si>
+  <si>
+    <t>Gm road</t>
+  </si>
+  <si>
+    <t>Jagadeep</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>jag@gmail.com</t>
+  </si>
+  <si>
+    <t>Am road</t>
+  </si>
+  <si>
+    <t>Pm road</t>
+  </si>
+  <si>
+    <t>900021</t>
+  </si>
+  <si>
+    <t>789654</t>
+  </si>
+  <si>
+    <t>9687456213</t>
+  </si>
+  <si>
+    <t>9874563210</t>
+  </si>
+  <si>
+    <t>7896541</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -163,6 +220,14 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -189,10 +254,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -496,7 +563,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -510,7 +577,7 @@
     <col min="10" max="10" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -541,8 +608,11 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="3" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -573,8 +643,11 @@
       <c r="J2" t="s">
         <v>19</v>
       </c>
+      <c r="K2" t="s">
+        <v>41</v>
+      </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -605,8 +678,11 @@
       <c r="J3" t="s">
         <v>28</v>
       </c>
+      <c r="K3" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>38</v>
       </c>
@@ -628,8 +704,11 @@
       <c r="I4" t="s">
         <v>31</v>
       </c>
+      <c r="K4" t="s">
+        <v>43</v>
+      </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>32</v>
       </c>
@@ -650,11 +729,83 @@
       </c>
       <c r="I5" t="s">
         <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" t="s">
+        <v>47</v>
+      </c>
+      <c r="G6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="K6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" t="s">
+        <v>52</v>
+      </c>
+      <c r="G7" t="s">
+        <v>53</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="K7" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C4" r:id="rId1" xr:uid="{438B0C51-3939-4999-8ED8-82C7214F3764}"/>
+    <hyperlink ref="C6" r:id="rId2" xr:uid="{3BF7A0A5-6552-46E1-838A-D9D68EB2D251}"/>
+    <hyperlink ref="C7" r:id="rId3" xr:uid="{D02C06B4-F1FE-47EE-8B4B-A719E1531DD9}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
